--- a/EXEMPLE_Entrada_Mes_Demo.xlsx
+++ b/EXEMPLE_Entrada_Mes_Demo.xlsx
@@ -1848,8 +1848,6 @@
       <c r="A53" s="4" t="n"/>
       <c r="B53" s="4" t="n"/>
     </row>
-    <row r="54"/>
-    <row r="55"/>
     <row r="56">
       <c r="A56" s="7" t="n"/>
     </row>
@@ -1878,10 +1876,10 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B4:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Valor no vàlid" promptTitle="Rol del professional" prompt="rotador = participa a la roda alfabètica&#10;fix-només = només cobreix torns fixos&#10;fix-i-rota = té torn fix i també rota&#10;sun-nit-only = només diumenge nit&#10;weekend-day-only = només dissabte/diumenge dia&#10;nou-incorporat = només dimecres 16-20 (excepte 1r del mes)" type="list">
+    <dataValidation sqref="B4:B200" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Rol no vàlid" error="Trieu una de les opcions del desplegable" promptTitle="Rol" prompt="Trieu el rol del professional" type="list">
       <formula1>"rotador,fix-només,fix-i-rota,sun-nit-only,weekend-day-only,nou-incorporat"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="Actiu" prompt="Sí o No" type="list">
+    <dataValidation sqref="E4:E200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no vàlid" error="Trieu Sí o No" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
